--- a/scraper/downloads/projects_page_4.xlsx
+++ b/scraper/downloads/projects_page_4.xlsx
@@ -201,7 +201,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <cols>
-    <col min="1" max="1" width="22.950000000000003" customWidth="1"/>
+    <col min="1" max="1" width="8.100000000000001" customWidth="1"/>
     <col min="2" max="2" width="6.75" customWidth="1"/>
     <col min="3" max="3" width="10.8" customWidth="1"/>
     <col min="4" max="4" width="9.450000000000001" customWidth="1"/>
@@ -212,14 +212,14 @@
     <col min="9" max="9" width="10.8" customWidth="1"/>
     <col min="10" max="10" width="6.75" customWidth="1"/>
     <col min="11" max="11" width="8.100000000000001" customWidth="1"/>
-    <col min="12" max="12" width="18.900000000000002" customWidth="1"/>
+    <col min="12" max="12" width="12.15" customWidth="1"/>
     <col min="13" max="13" width="6.75" customWidth="1"/>
     <col min="14" max="14" width="14.850000000000001" customWidth="1"/>
     <col min="15" max="15" width="28.35" customWidth="1"/>
     <col min="16" max="16" width="13.5" customWidth="1"/>
-    <col min="17" max="17" width="10.8" customWidth="1"/>
+    <col min="17" max="17" width="27" customWidth="1"/>
     <col min="18" max="18" width="6.75" customWidth="1"/>
-    <col min="19" max="19" width="13.5" customWidth="1"/>
+    <col min="19" max="19" width="14.850000000000001" customWidth="1"/>
     <col min="20" max="20" width="21.6" customWidth="1"/>
   </cols>
   <sheetData>
@@ -342,7 +342,7 @@
         <v>15</v>
       </c>
       <c r="C3" s="65">
-        <v>56</v>
+        <v>29</v>
       </c>
       <c t="inlineStr" r="D3">
         <is>
@@ -351,31 +351,31 @@
       </c>
       <c t="inlineStr" r="E3">
         <is>
-          <t xml:space="preserve">mecher 2023-דירות 46-56-66 טיפוס D2</t>
+          <t xml:space="preserve">mecher 2023-דירה 29 טיפוס G1</t>
         </is>
       </c>
       <c r="F3" s="65">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G3" s="65">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H3" s="65">
-        <v>89</v>
-      </c>
-      <c t="n" r="I3">
-        <v>6.2</v>
+        <v>55</v>
+      </c>
+      <c r="I3" s="65">
+        <v>0</v>
       </c>
       <c t="inlineStr" r="L3">
         <is>
-          <t xml:space="preserve">מזרח </t>
-        </is>
-      </c>
-      <c r="N3" s="63">
-        <v>5770000</v>
-      </c>
-      <c r="O3" s="63">
-        <v>5770000</v>
+          <t xml:space="preserve">דרום </t>
+        </is>
+      </c>
+      <c r="N3" s="65">
+        <v>0</v>
+      </c>
+      <c r="O3" s="65">
+        <v>0</v>
       </c>
       <c t="inlineStr" r="R3">
         <is>
@@ -393,7 +393,7 @@
         <v>15</v>
       </c>
       <c r="C4" s="65">
-        <v>58</v>
+        <v>30</v>
       </c>
       <c t="inlineStr" r="D4">
         <is>
@@ -402,31 +402,31 @@
       </c>
       <c t="inlineStr" r="E4">
         <is>
-          <t xml:space="preserve">mecher 2023-דירות 38-48-58-68 טיפוס F3</t>
+          <t xml:space="preserve">mecher 2023-דירה 30 טיפוס H1</t>
         </is>
       </c>
       <c r="F4" s="65">
-        <v>6</v>
-      </c>
-      <c r="G4" s="65">
-        <v>2</v>
+        <v>3</v>
+      </c>
+      <c t="n" r="G4">
+        <v>3.5</v>
       </c>
       <c r="H4" s="65">
-        <v>53</v>
+        <v>94</v>
       </c>
       <c t="n" r="I4">
-        <v>5.9</v>
+        <v>3.4</v>
       </c>
       <c t="inlineStr" r="L4">
         <is>
-          <t xml:space="preserve">דרום </t>
+          <t xml:space="preserve">דרום מערב </t>
         </is>
       </c>
       <c r="N4" s="63">
-        <v>4380000</v>
+        <v>5340000</v>
       </c>
       <c r="O4" s="63">
-        <v>4380000</v>
+        <v>5340000</v>
       </c>
       <c t="inlineStr" r="R4">
         <is>
@@ -444,7 +444,7 @@
         <v>15</v>
       </c>
       <c r="C5" s="65">
-        <v>59</v>
+        <v>31</v>
       </c>
       <c t="inlineStr" r="D5">
         <is>
@@ -453,31 +453,31 @@
       </c>
       <c t="inlineStr" r="E5">
         <is>
-          <t xml:space="preserve">mecher 2023-דירות 39-49-59-69 טיפוס G2</t>
+          <t xml:space="preserve">mecher 2023-דירות 1-11-21-31-41-51-61 טיפוס A</t>
         </is>
       </c>
       <c r="F5" s="65">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G5" s="65">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H5" s="65">
-        <v>54</v>
+        <v>88</v>
       </c>
       <c t="n" r="I5">
-        <v>4.2</v>
+        <v>6.4</v>
       </c>
       <c t="inlineStr" r="L5">
         <is>
-          <t xml:space="preserve">דרום </t>
+          <t xml:space="preserve">צפון מערב </t>
         </is>
       </c>
       <c r="N5" s="63">
-        <v>4380000</v>
+        <v>5210000</v>
       </c>
       <c r="O5" s="63">
-        <v>4380000</v>
+        <v>5210000</v>
       </c>
       <c t="inlineStr" r="R5">
         <is>
@@ -495,7 +495,7 @@
         <v>15</v>
       </c>
       <c r="C6" s="65">
-        <v>61</v>
+        <v>33</v>
       </c>
       <c t="inlineStr" r="D6">
         <is>
@@ -504,31 +504,31 @@
       </c>
       <c t="inlineStr" r="E6">
         <is>
-          <t xml:space="preserve">mecher 2023-דירות 1-11-21-31-41-51-61 טיפוס A</t>
+          <t xml:space="preserve">mecher 2023-דירות 3-13-23-33-43-53-63 טיפוס B1</t>
         </is>
       </c>
       <c r="F6" s="65">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G6" s="65">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H6" s="65">
-        <v>88</v>
+        <v>53</v>
       </c>
       <c t="n" r="I6">
-        <v>6.4</v>
+        <v>6.5</v>
       </c>
       <c t="inlineStr" r="L6">
         <is>
-          <t xml:space="preserve">צפון מערב </t>
+          <t xml:space="preserve">צפון </t>
         </is>
       </c>
       <c r="N6" s="63">
-        <v>6380000</v>
+        <v>3780000</v>
       </c>
       <c r="O6" s="63">
-        <v>6380000</v>
+        <v>3780000</v>
       </c>
       <c t="inlineStr" r="R6">
         <is>
@@ -546,7 +546,7 @@
         <v>15</v>
       </c>
       <c r="C7" s="65">
-        <v>62</v>
+        <v>34</v>
       </c>
       <c t="inlineStr" r="D7">
         <is>
@@ -555,11 +555,11 @@
       </c>
       <c t="inlineStr" r="E7">
         <is>
-          <t xml:space="preserve">mecher 2023-דירות 2-12-22-32-42-52-62 טיפוס B</t>
+          <t xml:space="preserve">mecher 2023-דירות 4-14-24-34-44-54-64 טיפוס B2</t>
         </is>
       </c>
       <c r="F7" s="65">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G7" s="65">
         <v>2</v>
@@ -576,10 +576,10 @@
         </is>
       </c>
       <c r="N7" s="63">
-        <v>4270000</v>
+        <v>3770000</v>
       </c>
       <c r="O7" s="63">
-        <v>4270000</v>
+        <v>3770000</v>
       </c>
       <c t="inlineStr" r="R7">
         <is>
@@ -597,7 +597,7 @@
         <v>15</v>
       </c>
       <c r="C8" s="65">
-        <v>63</v>
+        <v>35</v>
       </c>
       <c t="inlineStr" r="D8">
         <is>
@@ -606,35 +606,53 @@
       </c>
       <c t="inlineStr" r="E8">
         <is>
-          <t xml:space="preserve">mecher 2023-דירות 3-13-23-33-43-53-63 טיפוס B1</t>
+          <t xml:space="preserve">mecher 2023-דירות 5-15-25-35-45-55-65 טיפוס C</t>
         </is>
       </c>
       <c r="F8" s="65">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G8" s="65">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H8" s="65">
-        <v>53</v>
+        <v>87</v>
       </c>
       <c t="n" r="I8">
-        <v>6.5</v>
+        <v>6.9</v>
       </c>
       <c t="inlineStr" r="L8">
         <is>
-          <t xml:space="preserve">צפון </t>
+          <t xml:space="preserve">מזרח </t>
         </is>
       </c>
       <c r="N8" s="63">
-        <v>4280000</v>
+        <v>5650000</v>
       </c>
       <c r="O8" s="63">
-        <v>4280000</v>
+        <v>5650000</v>
+      </c>
+      <c r="P8" s="63">
+        <v>6750000</v>
+      </c>
+      <c t="inlineStr" r="Q8">
+        <is>
+          <t xml:space="preserve">הרשמה: Daniel Bassan</t>
+        </is>
       </c>
       <c t="inlineStr" r="R8">
         <is>
-          <t xml:space="preserve">פעיל</t>
+          <t xml:space="preserve">הרשמה</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="S8">
+        <is>
+          <t xml:space="preserve">יניב אשכנזי</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="T8">
+        <is>
+          <t xml:space="preserve">30/03/2025</t>
         </is>
       </c>
     </row>
@@ -648,7 +666,7 @@
         <v>15</v>
       </c>
       <c r="C9" s="65">
-        <v>64</v>
+        <v>36</v>
       </c>
       <c t="inlineStr" r="D9">
         <is>
@@ -657,31 +675,31 @@
       </c>
       <c t="inlineStr" r="E9">
         <is>
-          <t xml:space="preserve">mecher 2023-דירות 4-14-24-34-44-54-64 טיפוס B2</t>
+          <t xml:space="preserve">mecher 2023-דירה 36 טיפוס D1</t>
         </is>
       </c>
       <c r="F9" s="65">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G9" s="65">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H9" s="65">
-        <v>53</v>
-      </c>
-      <c t="n" r="I9">
-        <v>6.5</v>
+        <v>89</v>
+      </c>
+      <c r="I9" s="65">
+        <v>0</v>
       </c>
       <c t="inlineStr" r="L9">
         <is>
-          <t xml:space="preserve">צפון </t>
-        </is>
-      </c>
-      <c r="N9" s="63">
-        <v>4270000</v>
-      </c>
-      <c r="O9" s="63">
-        <v>4270000</v>
+          <t xml:space="preserve">מזרח </t>
+        </is>
+      </c>
+      <c r="N9" s="65">
+        <v>0</v>
+      </c>
+      <c r="O9" s="65">
+        <v>0</v>
       </c>
       <c t="inlineStr" r="R9">
         <is>
@@ -699,7 +717,7 @@
         <v>15</v>
       </c>
       <c r="C10" s="65">
-        <v>65</v>
+        <v>37</v>
       </c>
       <c t="inlineStr" r="D10">
         <is>
@@ -708,31 +726,31 @@
       </c>
       <c t="inlineStr" r="E10">
         <is>
-          <t xml:space="preserve">mecher 2023-דירות 5-15-25-35-45-55-65 טיפוס C</t>
+          <t xml:space="preserve">mecher 2023-דירות 37-47-57-67 טיפוס E2</t>
         </is>
       </c>
       <c r="F10" s="65">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G10" s="65">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H10" s="65">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c t="n" r="I10">
-        <v>6.9</v>
+        <v>10.1</v>
       </c>
       <c t="inlineStr" r="L10">
         <is>
-          <t xml:space="preserve">מזרח </t>
+          <t xml:space="preserve">דרום מזרח </t>
         </is>
       </c>
       <c r="N10" s="63">
-        <v>7310000</v>
+        <v>5810000</v>
       </c>
       <c r="O10" s="63">
-        <v>7310000</v>
+        <v>5810000</v>
       </c>
       <c t="inlineStr" r="R10">
         <is>
@@ -750,7 +768,7 @@
         <v>15</v>
       </c>
       <c r="C11" s="65">
-        <v>66</v>
+        <v>38</v>
       </c>
       <c t="inlineStr" r="D11">
         <is>
@@ -759,31 +777,31 @@
       </c>
       <c t="inlineStr" r="E11">
         <is>
-          <t xml:space="preserve">mecher 2023-דירות 46-56-66 טיפוס D2</t>
+          <t xml:space="preserve">mecher 2023-דירות 38-48-58-68 טיפוס F3</t>
         </is>
       </c>
       <c r="F11" s="65">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G11" s="65">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H11" s="65">
-        <v>89</v>
+        <v>53</v>
       </c>
       <c t="n" r="I11">
-        <v>6.2</v>
+        <v>5.9</v>
       </c>
       <c t="inlineStr" r="L11">
         <is>
-          <t xml:space="preserve">מזרח </t>
+          <t xml:space="preserve">דרום </t>
         </is>
       </c>
       <c r="N11" s="63">
-        <v>7400000</v>
+        <v>4030000</v>
       </c>
       <c r="O11" s="63">
-        <v>7400000</v>
+        <v>4030000</v>
       </c>
       <c t="inlineStr" r="R11">
         <is>
@@ -801,7 +819,7 @@
         <v>15</v>
       </c>
       <c r="C12" s="65">
-        <v>67</v>
+        <v>39</v>
       </c>
       <c t="inlineStr" r="D12">
         <is>
@@ -810,31 +828,31 @@
       </c>
       <c t="inlineStr" r="E12">
         <is>
-          <t xml:space="preserve">mecher 2023-דירות 37-47-57-67 טיפוס E2</t>
+          <t xml:space="preserve">mecher 2023-דירות 39-49-59-69 טיפוס G2</t>
         </is>
       </c>
       <c r="F12" s="65">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G12" s="65">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H12" s="65">
-        <v>89</v>
+        <v>54</v>
       </c>
       <c t="n" r="I12">
-        <v>10.1</v>
+        <v>4.2</v>
       </c>
       <c t="inlineStr" r="L12">
         <is>
-          <t xml:space="preserve">דרום מזרח </t>
-        </is>
-      </c>
-      <c r="N12" s="63">
-        <v>7600000</v>
-      </c>
-      <c r="O12" s="63">
-        <v>7600000</v>
+          <t xml:space="preserve">דרום </t>
+        </is>
+      </c>
+      <c r="N12" s="65">
+        <v>0</v>
+      </c>
+      <c r="O12" s="65">
+        <v>0</v>
       </c>
       <c t="inlineStr" r="R12">
         <is>
@@ -852,7 +870,7 @@
         <v>15</v>
       </c>
       <c r="C13" s="65">
-        <v>68</v>
+        <v>40</v>
       </c>
       <c t="inlineStr" r="D13">
         <is>
@@ -861,31 +879,31 @@
       </c>
       <c t="inlineStr" r="E13">
         <is>
-          <t xml:space="preserve">mecher 2023-דירות 38-48-58-68 טיפוס F3</t>
+          <t xml:space="preserve">mecher 2023-דירות 40,50,60,70 טיפוס H2</t>
         </is>
       </c>
       <c r="F13" s="65">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G13" s="65">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H13" s="65">
-        <v>53</v>
+        <v>93</v>
       </c>
       <c t="n" r="I13">
-        <v>5.9</v>
+        <v>8.1</v>
       </c>
       <c t="inlineStr" r="L13">
         <is>
-          <t xml:space="preserve">דרום </t>
+          <t xml:space="preserve">דרום מערב </t>
         </is>
       </c>
       <c r="N13" s="63">
-        <v>4550000</v>
+        <v>5550000</v>
       </c>
       <c r="O13" s="63">
-        <v>4550000</v>
+        <v>5550000</v>
       </c>
       <c t="inlineStr" r="R13">
         <is>
@@ -903,7 +921,7 @@
         <v>15</v>
       </c>
       <c r="C14" s="65">
-        <v>69</v>
+        <v>41</v>
       </c>
       <c t="inlineStr" r="D14">
         <is>
@@ -912,31 +930,31 @@
       </c>
       <c t="inlineStr" r="E14">
         <is>
-          <t xml:space="preserve">mecher 2023-דירות 39-49-59-69 טיפוס G2</t>
+          <t xml:space="preserve">mecher 2023-דירות 1-11-21-31-41-51-61 טיפוס A</t>
         </is>
       </c>
       <c r="F14" s="65">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G14" s="65">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H14" s="65">
-        <v>54</v>
+        <v>88</v>
       </c>
       <c t="n" r="I14">
-        <v>4.2</v>
+        <v>6.4</v>
       </c>
       <c t="inlineStr" r="L14">
         <is>
-          <t xml:space="preserve">דרום </t>
+          <t xml:space="preserve">צפון מערב </t>
         </is>
       </c>
       <c r="N14" s="63">
-        <v>4540000</v>
+        <v>5360000</v>
       </c>
       <c r="O14" s="63">
-        <v>4540000</v>
+        <v>5360000</v>
       </c>
       <c t="inlineStr" r="R14">
         <is>
@@ -954,7 +972,7 @@
         <v>15</v>
       </c>
       <c r="C15" s="65">
-        <v>70</v>
+        <v>42</v>
       </c>
       <c t="inlineStr" r="D15">
         <is>
@@ -963,31 +981,31 @@
       </c>
       <c t="inlineStr" r="E15">
         <is>
-          <t xml:space="preserve">mecher 2023-דירות 40,50,60,70 טיפוס H2</t>
+          <t xml:space="preserve">mecher 2023-דירות 2-12-22-32-42-52-62 טיפוס B</t>
         </is>
       </c>
       <c r="F15" s="65">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G15" s="65">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H15" s="65">
-        <v>93</v>
+        <v>53</v>
       </c>
       <c t="n" r="I15">
-        <v>8.1</v>
+        <v>6.5</v>
       </c>
       <c t="inlineStr" r="L15">
         <is>
-          <t xml:space="preserve">דרום מערב </t>
+          <t xml:space="preserve">צפון </t>
         </is>
       </c>
       <c r="N15" s="63">
-        <v>7890000</v>
+        <v>3940000</v>
       </c>
       <c r="O15" s="63">
-        <v>7890000</v>
+        <v>3940000</v>
       </c>
       <c t="inlineStr" r="R15">
         <is>
@@ -1005,35 +1023,40 @@
         <v>15</v>
       </c>
       <c r="C16" s="65">
-        <v>71</v>
+        <v>43</v>
       </c>
       <c t="inlineStr" r="D16">
         <is>
           <t xml:space="preserve">דירה</t>
         </is>
       </c>
+      <c t="inlineStr" r="E16">
+        <is>
+          <t xml:space="preserve">mecher 2023-דירות 3-13-23-33-43-53-63 טיפוס B1</t>
+        </is>
+      </c>
       <c r="F16" s="65">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G16" s="65">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H16" s="65">
-        <v>166</v>
-      </c>
-      <c r="I16" s="65">
-        <v>14</v>
+        <v>53</v>
+      </c>
+      <c t="n" r="I16">
+        <v>6.5</v>
       </c>
       <c t="inlineStr" r="L16">
         <is>
-          <t xml:space="preserve">צפון דרום מערב </t>
+          <t xml:space="preserve">צפון </t>
         </is>
       </c>
       <c r="N16" s="63">
-        <v>15750000</v>
+        <v>3940000</v>
       </c>
       <c r="O16" s="63">
-        <v>15750000</v>
+        <v>3940000</v>
       </c>
       <c t="inlineStr" r="R16">
         <is>
@@ -1051,24 +1074,29 @@
         <v>15</v>
       </c>
       <c r="C17" s="65">
-        <v>72</v>
+        <v>44</v>
       </c>
       <c t="inlineStr" r="D17">
         <is>
           <t xml:space="preserve">דירה</t>
         </is>
       </c>
+      <c t="inlineStr" r="E17">
+        <is>
+          <t xml:space="preserve">mecher 2023-דירות 4-14-24-34-44-54-64 טיפוס B2</t>
+        </is>
+      </c>
       <c r="F17" s="65">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G17" s="65">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H17" s="65">
-        <v>150</v>
-      </c>
-      <c r="I17" s="65">
-        <v>14</v>
+        <v>53</v>
+      </c>
+      <c t="n" r="I17">
+        <v>6.5</v>
       </c>
       <c t="inlineStr" r="L17">
         <is>
@@ -1076,10 +1104,10 @@
         </is>
       </c>
       <c r="N17" s="63">
-        <v>14320000</v>
+        <v>3940000</v>
       </c>
       <c r="O17" s="63">
-        <v>14320000</v>
+        <v>3940000</v>
       </c>
       <c t="inlineStr" r="R17">
         <is>
@@ -1097,35 +1125,40 @@
         <v>15</v>
       </c>
       <c r="C18" s="65">
-        <v>73</v>
+        <v>45</v>
       </c>
       <c t="inlineStr" r="D18">
         <is>
           <t xml:space="preserve">דירה</t>
         </is>
       </c>
+      <c t="inlineStr" r="E18">
+        <is>
+          <t xml:space="preserve">mecher 2023-דירות 5-15-25-35-45-55-65 טיפוס C</t>
+        </is>
+      </c>
       <c r="F18" s="65">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G18" s="65">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H18" s="65">
-        <v>150</v>
-      </c>
-      <c r="I18" s="65">
-        <v>28</v>
+        <v>87</v>
+      </c>
+      <c t="n" r="I18">
+        <v>6.9</v>
       </c>
       <c t="inlineStr" r="L18">
         <is>
-          <t xml:space="preserve">צפון </t>
+          <t xml:space="preserve">מזרח </t>
         </is>
       </c>
       <c r="N18" s="63">
-        <v>14900000</v>
+        <v>5800000</v>
       </c>
       <c r="O18" s="63">
-        <v>14900000</v>
+        <v>5800000</v>
       </c>
       <c t="inlineStr" r="R18">
         <is>
@@ -1143,35 +1176,40 @@
         <v>15</v>
       </c>
       <c r="C19" s="65">
-        <v>74</v>
+        <v>46</v>
       </c>
       <c t="inlineStr" r="D19">
         <is>
           <t xml:space="preserve">דירה</t>
         </is>
       </c>
+      <c t="inlineStr" r="E19">
+        <is>
+          <t xml:space="preserve">mecher 2023-דירות 46-56-66 טיפוס D2</t>
+        </is>
+      </c>
       <c r="F19" s="65">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G19" s="65">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H19" s="65">
-        <v>164</v>
-      </c>
-      <c r="I19" s="65">
-        <v>86</v>
+        <v>89</v>
+      </c>
+      <c t="n" r="I19">
+        <v>6.2</v>
       </c>
       <c t="inlineStr" r="L19">
         <is>
-          <t xml:space="preserve">צפון מזרח </t>
+          <t xml:space="preserve">מזרח </t>
         </is>
       </c>
       <c r="N19" s="63">
-        <v>19700000</v>
+        <v>5200000</v>
       </c>
       <c r="O19" s="63">
-        <v>19700000</v>
+        <v>5200000</v>
       </c>
       <c t="inlineStr" r="R19">
         <is>
@@ -1189,35 +1227,40 @@
         <v>15</v>
       </c>
       <c r="C20" s="65">
-        <v>75</v>
+        <v>47</v>
       </c>
       <c t="inlineStr" r="D20">
         <is>
           <t xml:space="preserve">דירה</t>
         </is>
       </c>
+      <c t="inlineStr" r="E20">
+        <is>
+          <t xml:space="preserve">mecher 2023-דירות 37-47-57-67 טיפוס E2</t>
+        </is>
+      </c>
       <c r="F20" s="65">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G20" s="65">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H20" s="65">
-        <v>162</v>
-      </c>
-      <c r="I20" s="65">
-        <v>64</v>
+        <v>89</v>
+      </c>
+      <c t="n" r="I20">
+        <v>10.1</v>
       </c>
       <c t="inlineStr" r="L20">
         <is>
-          <t xml:space="preserve">מזרח </t>
+          <t xml:space="preserve">דרום מזרח </t>
         </is>
       </c>
       <c r="N20" s="63">
-        <v>18580000</v>
+        <v>5520000</v>
       </c>
       <c r="O20" s="63">
-        <v>18580000</v>
+        <v>5520000</v>
       </c>
       <c t="inlineStr" r="R20">
         <is>
@@ -1235,35 +1278,40 @@
         <v>15</v>
       </c>
       <c r="C21" s="65">
-        <v>76</v>
+        <v>48</v>
       </c>
       <c t="inlineStr" r="D21">
         <is>
           <t xml:space="preserve">דירה</t>
         </is>
       </c>
+      <c t="inlineStr" r="E21">
+        <is>
+          <t xml:space="preserve">mecher 2023-דירות 38-48-58-68 טיפוס F3</t>
+        </is>
+      </c>
       <c r="F21" s="65">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G21" s="65">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H21" s="65">
-        <v>166</v>
-      </c>
-      <c r="I21" s="65">
-        <v>86</v>
+        <v>53</v>
+      </c>
+      <c t="n" r="I21">
+        <v>5.9</v>
       </c>
       <c t="inlineStr" r="L21">
         <is>
-          <t xml:space="preserve">דרום מזרח </t>
+          <t xml:space="preserve">דרום </t>
         </is>
       </c>
       <c r="N21" s="63">
-        <v>19950000</v>
+        <v>3900000</v>
       </c>
       <c r="O21" s="63">
-        <v>19950000</v>
+        <v>3900000</v>
       </c>
       <c t="inlineStr" r="R21">
         <is>
@@ -1281,24 +1329,29 @@
         <v>15</v>
       </c>
       <c r="C22" s="65">
-        <v>77</v>
+        <v>49</v>
       </c>
       <c t="inlineStr" r="D22">
         <is>
           <t xml:space="preserve">דירה</t>
         </is>
       </c>
+      <c t="inlineStr" r="E22">
+        <is>
+          <t xml:space="preserve">mecher 2023-דירות 39-49-59-69 טיפוס G2</t>
+        </is>
+      </c>
       <c r="F22" s="65">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G22" s="65">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H22" s="65">
-        <v>200</v>
-      </c>
-      <c r="I22" s="65">
-        <v>62</v>
+        <v>54</v>
+      </c>
+      <c t="n" r="I22">
+        <v>4.2</v>
       </c>
       <c t="inlineStr" r="L22">
         <is>
@@ -1306,10 +1359,10 @@
         </is>
       </c>
       <c r="N22" s="63">
-        <v>21920000</v>
+        <v>4210000</v>
       </c>
       <c r="O22" s="63">
-        <v>21920000</v>
+        <v>4210000</v>
       </c>
       <c t="inlineStr" r="R22">
         <is>
@@ -1327,24 +1380,29 @@
         <v>15</v>
       </c>
       <c r="C23" s="65">
-        <v>78</v>
+        <v>50</v>
       </c>
       <c t="inlineStr" r="D23">
         <is>
           <t xml:space="preserve">דירה</t>
         </is>
       </c>
+      <c t="inlineStr" r="E23">
+        <is>
+          <t xml:space="preserve">mecher 2023-דירות 40,50,60,70 טיפוס H2</t>
+        </is>
+      </c>
       <c r="F23" s="65">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G23" s="65">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H23" s="65">
-        <v>168</v>
-      </c>
-      <c r="I23" s="65">
-        <v>18</v>
+        <v>93</v>
+      </c>
+      <c t="n" r="I23">
+        <v>8.1</v>
       </c>
       <c t="inlineStr" r="L23">
         <is>
@@ -1352,58 +1410,79 @@
         </is>
       </c>
       <c r="N23" s="63">
-        <v>16690000</v>
+        <v>5700000</v>
       </c>
       <c r="O23" s="63">
-        <v>16690000</v>
+        <v>5700000</v>
+      </c>
+      <c r="P23" s="63">
+        <v>6990000</v>
+      </c>
+      <c t="inlineStr" r="Q23">
+        <is>
+          <t xml:space="preserve">הרשמה: משה</t>
+        </is>
       </c>
       <c t="inlineStr" r="R23">
         <is>
-          <t xml:space="preserve">פעיל</t>
+          <t xml:space="preserve">הרשמה</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="S23">
+        <is>
+          <t xml:space="preserve">אהרון אברהם</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="T23">
+        <is>
+          <t xml:space="preserve">24/05/2026</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c t="inlineStr" r="A24">
         <is>
-          <t xml:space="preserve">שמואל הנגיד-רזדנס</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="B24">
-        <is>
-          <t xml:space="preserve">27-1</t>
-        </is>
+          <t xml:space="preserve">עדן</t>
+        </is>
+      </c>
+      <c r="B24" s="65">
+        <v>15</v>
       </c>
       <c r="C24" s="65">
-        <v>1</v>
+        <v>51</v>
       </c>
       <c t="inlineStr" r="D24">
         <is>
-          <t xml:space="preserve">דירת גן</t>
+          <t xml:space="preserve">דירה</t>
         </is>
       </c>
       <c t="inlineStr" r="E24">
         <is>
-          <t xml:space="preserve">b1 apt 1</t>
+          <t xml:space="preserve">mecher 2023-דירות 1-11-21-31-41-51-61 טיפוס A</t>
         </is>
       </c>
       <c r="F24" s="65">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G24" s="65">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H24" s="65">
-        <v>69</v>
-      </c>
-      <c r="I24" s="65">
-        <v>35</v>
+        <v>88</v>
+      </c>
+      <c t="n" r="I24">
+        <v>6.4</v>
+      </c>
+      <c t="inlineStr" r="L24">
+        <is>
+          <t xml:space="preserve">צפון מערב </t>
+        </is>
       </c>
       <c r="N24" s="63">
-        <v>4530240</v>
+        <v>5510000</v>
       </c>
       <c r="O24" s="63">
-        <v>4530240</v>
+        <v>5510000</v>
       </c>
       <c t="inlineStr" r="R24">
         <is>
@@ -1414,64 +1493,65 @@
     <row r="25">
       <c t="inlineStr" r="A25">
         <is>
-          <t xml:space="preserve">שמואל הנגיד-רזדנס</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="B25">
-        <is>
-          <t xml:space="preserve">27-1</t>
-        </is>
+          <t xml:space="preserve">עדן</t>
+        </is>
+      </c>
+      <c r="B25" s="65">
+        <v>15</v>
       </c>
       <c r="C25" s="65">
+        <v>52</v>
+      </c>
+      <c t="inlineStr" r="D25">
+        <is>
+          <t xml:space="preserve">דירה</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="E25">
+        <is>
+          <t xml:space="preserve">mecher 2023-דירות 2-12-22-32-42-52-62 טיפוס B</t>
+        </is>
+      </c>
+      <c r="F25" s="65">
+        <v>6</v>
+      </c>
+      <c r="G25" s="65">
         <v>2</v>
       </c>
-      <c t="inlineStr" r="D25">
-        <is>
-          <t xml:space="preserve">דירה</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="E25">
-        <is>
-          <t xml:space="preserve">b1 apt 2</t>
-        </is>
-      </c>
-      <c r="F25" s="65">
-        <v>2</v>
-      </c>
-      <c r="G25" s="65">
-        <v>3</v>
-      </c>
       <c r="H25" s="65">
-        <v>76</v>
-      </c>
-      <c r="I25" s="65">
-        <v>7</v>
+        <v>53</v>
+      </c>
+      <c t="n" r="I25">
+        <v>6.5</v>
+      </c>
+      <c t="inlineStr" r="L25">
+        <is>
+          <t xml:space="preserve">צפון </t>
+        </is>
       </c>
       <c r="N25" s="63">
-        <v>4293000</v>
+        <v>4100000</v>
       </c>
       <c r="O25" s="63">
-        <v>4293000</v>
+        <v>4100000</v>
       </c>
       <c t="inlineStr" r="R25">
         <is>
-          <t xml:space="preserve">מו״מ</t>
+          <t xml:space="preserve">פעיל</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c t="inlineStr" r="A26">
         <is>
-          <t xml:space="preserve">שמואל הנגיד-רזדנס</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="B26">
-        <is>
-          <t xml:space="preserve">27-1</t>
-        </is>
+          <t xml:space="preserve">עדן</t>
+        </is>
+      </c>
+      <c r="B26" s="65">
+        <v>15</v>
       </c>
       <c r="C26" s="65">
-        <v>3</v>
+        <v>53</v>
       </c>
       <c t="inlineStr" r="D26">
         <is>
@@ -1480,26 +1560,31 @@
       </c>
       <c t="inlineStr" r="E26">
         <is>
-          <t xml:space="preserve">b1 apt 3</t>
+          <t xml:space="preserve">mecher 2023-דירות 3-13-23-33-43-53-63 טיפוס B1</t>
         </is>
       </c>
       <c r="F26" s="65">
+        <v>6</v>
+      </c>
+      <c r="G26" s="65">
         <v>2</v>
       </c>
-      <c r="G26" s="65">
-        <v>3</v>
-      </c>
       <c r="H26" s="65">
-        <v>75</v>
-      </c>
-      <c r="I26" s="65">
-        <v>10</v>
+        <v>53</v>
+      </c>
+      <c t="n" r="I26">
+        <v>6.5</v>
+      </c>
+      <c t="inlineStr" r="L26">
+        <is>
+          <t xml:space="preserve">צפון </t>
+        </is>
       </c>
       <c r="N26" s="63">
-        <v>4320000</v>
+        <v>4110000</v>
       </c>
       <c r="O26" s="63">
-        <v>4320000</v>
+        <v>4110000</v>
       </c>
       <c t="inlineStr" r="R26">
         <is>
@@ -1510,16 +1595,14 @@
     <row r="27">
       <c t="inlineStr" r="A27">
         <is>
-          <t xml:space="preserve">שמואל הנגיד-רזדנס</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="B27">
-        <is>
-          <t xml:space="preserve">27-1</t>
-        </is>
+          <t xml:space="preserve">עדן</t>
+        </is>
+      </c>
+      <c r="B27" s="65">
+        <v>15</v>
       </c>
       <c r="C27" s="65">
-        <v>4</v>
+        <v>54</v>
       </c>
       <c t="inlineStr" r="D27">
         <is>
@@ -1528,26 +1611,31 @@
       </c>
       <c t="inlineStr" r="E27">
         <is>
-          <t xml:space="preserve">b1 apt 4</t>
+          <t xml:space="preserve">mecher 2023-דירות 4-14-24-34-44-54-64 טיפוס B2</t>
         </is>
       </c>
       <c r="F27" s="65">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G27" s="65">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H27" s="65">
-        <v>76</v>
-      </c>
-      <c r="I27" s="65">
-        <v>7</v>
+        <v>53</v>
+      </c>
+      <c t="n" r="I27">
+        <v>6.5</v>
+      </c>
+      <c t="inlineStr" r="L27">
+        <is>
+          <t xml:space="preserve">צפון </t>
+        </is>
       </c>
       <c r="N27" s="63">
-        <v>4378860</v>
+        <v>4100000</v>
       </c>
       <c r="O27" s="63">
-        <v>4378860</v>
+        <v>4100000</v>
       </c>
       <c t="inlineStr" r="R27">
         <is>

--- a/scraper/downloads/projects_page_4.xlsx
+++ b/scraper/downloads/projects_page_4.xlsx
@@ -201,7 +201,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <cols>
-    <col min="1" max="1" width="8.100000000000001" customWidth="1"/>
+    <col min="1" max="1" width="22.950000000000003" customWidth="1"/>
     <col min="2" max="2" width="6.75" customWidth="1"/>
     <col min="3" max="3" width="10.8" customWidth="1"/>
     <col min="4" max="4" width="9.450000000000001" customWidth="1"/>
@@ -212,14 +212,14 @@
     <col min="9" max="9" width="10.8" customWidth="1"/>
     <col min="10" max="10" width="6.75" customWidth="1"/>
     <col min="11" max="11" width="8.100000000000001" customWidth="1"/>
-    <col min="12" max="12" width="12.15" customWidth="1"/>
+    <col min="12" max="12" width="18.900000000000002" customWidth="1"/>
     <col min="13" max="13" width="6.75" customWidth="1"/>
     <col min="14" max="14" width="14.850000000000001" customWidth="1"/>
     <col min="15" max="15" width="28.35" customWidth="1"/>
     <col min="16" max="16" width="13.5" customWidth="1"/>
-    <col min="17" max="17" width="27" customWidth="1"/>
+    <col min="17" max="17" width="10.8" customWidth="1"/>
     <col min="18" max="18" width="6.75" customWidth="1"/>
-    <col min="19" max="19" width="14.850000000000001" customWidth="1"/>
+    <col min="19" max="19" width="13.5" customWidth="1"/>
     <col min="20" max="20" width="21.6" customWidth="1"/>
   </cols>
   <sheetData>
@@ -342,7 +342,7 @@
         <v>15</v>
       </c>
       <c r="C3" s="65">
-        <v>29</v>
+        <v>56</v>
       </c>
       <c t="inlineStr" r="D3">
         <is>
@@ -351,31 +351,31 @@
       </c>
       <c t="inlineStr" r="E3">
         <is>
-          <t xml:space="preserve">mecher 2023-דירה 29 טיפוס G1</t>
+          <t xml:space="preserve">mecher 2023-דירות 46-56-66 טיפוס D2</t>
         </is>
       </c>
       <c r="F3" s="65">
+        <v>6</v>
+      </c>
+      <c r="G3" s="65">
         <v>3</v>
       </c>
-      <c r="G3" s="65">
-        <v>2</v>
-      </c>
       <c r="H3" s="65">
-        <v>55</v>
-      </c>
-      <c r="I3" s="65">
-        <v>0</v>
+        <v>89</v>
+      </c>
+      <c t="n" r="I3">
+        <v>6.2</v>
       </c>
       <c t="inlineStr" r="L3">
         <is>
-          <t xml:space="preserve">דרום </t>
-        </is>
-      </c>
-      <c r="N3" s="65">
-        <v>0</v>
-      </c>
-      <c r="O3" s="65">
-        <v>0</v>
+          <t xml:space="preserve">מזרח </t>
+        </is>
+      </c>
+      <c r="N3" s="63">
+        <v>5770000</v>
+      </c>
+      <c r="O3" s="63">
+        <v>5770000</v>
       </c>
       <c t="inlineStr" r="R3">
         <is>
@@ -393,7 +393,7 @@
         <v>15</v>
       </c>
       <c r="C4" s="65">
-        <v>30</v>
+        <v>58</v>
       </c>
       <c t="inlineStr" r="D4">
         <is>
@@ -402,31 +402,31 @@
       </c>
       <c t="inlineStr" r="E4">
         <is>
-          <t xml:space="preserve">mecher 2023-דירה 30 טיפוס H1</t>
+          <t xml:space="preserve">mecher 2023-דירות 38-48-58-68 טיפוס F3</t>
         </is>
       </c>
       <c r="F4" s="65">
-        <v>3</v>
-      </c>
-      <c t="n" r="G4">
-        <v>3.5</v>
+        <v>6</v>
+      </c>
+      <c r="G4" s="65">
+        <v>2</v>
       </c>
       <c r="H4" s="65">
-        <v>94</v>
+        <v>53</v>
       </c>
       <c t="n" r="I4">
-        <v>3.4</v>
+        <v>5.9</v>
       </c>
       <c t="inlineStr" r="L4">
         <is>
-          <t xml:space="preserve">דרום מערב </t>
+          <t xml:space="preserve">דרום </t>
         </is>
       </c>
       <c r="N4" s="63">
-        <v>5340000</v>
+        <v>4380000</v>
       </c>
       <c r="O4" s="63">
-        <v>5340000</v>
+        <v>4380000</v>
       </c>
       <c t="inlineStr" r="R4">
         <is>
@@ -444,7 +444,7 @@
         <v>15</v>
       </c>
       <c r="C5" s="65">
-        <v>31</v>
+        <v>59</v>
       </c>
       <c t="inlineStr" r="D5">
         <is>
@@ -453,31 +453,31 @@
       </c>
       <c t="inlineStr" r="E5">
         <is>
-          <t xml:space="preserve">mecher 2023-דירות 1-11-21-31-41-51-61 טיפוס A</t>
+          <t xml:space="preserve">mecher 2023-דירות 39-49-59-69 טיפוס G2</t>
         </is>
       </c>
       <c r="F5" s="65">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G5" s="65">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H5" s="65">
-        <v>88</v>
+        <v>54</v>
       </c>
       <c t="n" r="I5">
-        <v>6.4</v>
+        <v>4.2</v>
       </c>
       <c t="inlineStr" r="L5">
         <is>
-          <t xml:space="preserve">צפון מערב </t>
+          <t xml:space="preserve">דרום </t>
         </is>
       </c>
       <c r="N5" s="63">
-        <v>5210000</v>
+        <v>4380000</v>
       </c>
       <c r="O5" s="63">
-        <v>5210000</v>
+        <v>4380000</v>
       </c>
       <c t="inlineStr" r="R5">
         <is>
@@ -495,7 +495,7 @@
         <v>15</v>
       </c>
       <c r="C6" s="65">
-        <v>33</v>
+        <v>61</v>
       </c>
       <c t="inlineStr" r="D6">
         <is>
@@ -504,31 +504,31 @@
       </c>
       <c t="inlineStr" r="E6">
         <is>
-          <t xml:space="preserve">mecher 2023-דירות 3-13-23-33-43-53-63 טיפוס B1</t>
+          <t xml:space="preserve">mecher 2023-דירות 1-11-21-31-41-51-61 טיפוס A</t>
         </is>
       </c>
       <c r="F6" s="65">
+        <v>7</v>
+      </c>
+      <c r="G6" s="65">
         <v>4</v>
       </c>
-      <c r="G6" s="65">
-        <v>2</v>
-      </c>
       <c r="H6" s="65">
-        <v>53</v>
+        <v>88</v>
       </c>
       <c t="n" r="I6">
-        <v>6.5</v>
+        <v>6.4</v>
       </c>
       <c t="inlineStr" r="L6">
         <is>
-          <t xml:space="preserve">צפון </t>
+          <t xml:space="preserve">צפון מערב </t>
         </is>
       </c>
       <c r="N6" s="63">
-        <v>3780000</v>
+        <v>6380000</v>
       </c>
       <c r="O6" s="63">
-        <v>3780000</v>
+        <v>6380000</v>
       </c>
       <c t="inlineStr" r="R6">
         <is>
@@ -546,7 +546,7 @@
         <v>15</v>
       </c>
       <c r="C7" s="65">
-        <v>34</v>
+        <v>62</v>
       </c>
       <c t="inlineStr" r="D7">
         <is>
@@ -555,11 +555,11 @@
       </c>
       <c t="inlineStr" r="E7">
         <is>
-          <t xml:space="preserve">mecher 2023-דירות 4-14-24-34-44-54-64 טיפוס B2</t>
+          <t xml:space="preserve">mecher 2023-דירות 2-12-22-32-42-52-62 טיפוס B</t>
         </is>
       </c>
       <c r="F7" s="65">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G7" s="65">
         <v>2</v>
@@ -576,10 +576,10 @@
         </is>
       </c>
       <c r="N7" s="63">
-        <v>3770000</v>
+        <v>4270000</v>
       </c>
       <c r="O7" s="63">
-        <v>3770000</v>
+        <v>4270000</v>
       </c>
       <c t="inlineStr" r="R7">
         <is>
@@ -597,7 +597,7 @@
         <v>15</v>
       </c>
       <c r="C8" s="65">
-        <v>35</v>
+        <v>63</v>
       </c>
       <c t="inlineStr" r="D8">
         <is>
@@ -606,53 +606,35 @@
       </c>
       <c t="inlineStr" r="E8">
         <is>
-          <t xml:space="preserve">mecher 2023-דירות 5-15-25-35-45-55-65 טיפוס C</t>
+          <t xml:space="preserve">mecher 2023-דירות 3-13-23-33-43-53-63 טיפוס B1</t>
         </is>
       </c>
       <c r="F8" s="65">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G8" s="65">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H8" s="65">
-        <v>87</v>
+        <v>53</v>
       </c>
       <c t="n" r="I8">
-        <v>6.9</v>
+        <v>6.5</v>
       </c>
       <c t="inlineStr" r="L8">
         <is>
-          <t xml:space="preserve">מזרח </t>
+          <t xml:space="preserve">צפון </t>
         </is>
       </c>
       <c r="N8" s="63">
-        <v>5650000</v>
+        <v>4280000</v>
       </c>
       <c r="O8" s="63">
-        <v>5650000</v>
-      </c>
-      <c r="P8" s="63">
-        <v>6750000</v>
-      </c>
-      <c t="inlineStr" r="Q8">
-        <is>
-          <t xml:space="preserve">הרשמה: Daniel Bassan</t>
-        </is>
+        <v>4280000</v>
       </c>
       <c t="inlineStr" r="R8">
         <is>
-          <t xml:space="preserve">הרשמה</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="S8">
-        <is>
-          <t xml:space="preserve">יניב אשכנזי</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="T8">
-        <is>
-          <t xml:space="preserve">30/03/2025</t>
+          <t xml:space="preserve">פעיל</t>
         </is>
       </c>
     </row>
@@ -666,7 +648,7 @@
         <v>15</v>
       </c>
       <c r="C9" s="65">
-        <v>36</v>
+        <v>64</v>
       </c>
       <c t="inlineStr" r="D9">
         <is>
@@ -675,31 +657,31 @@
       </c>
       <c t="inlineStr" r="E9">
         <is>
-          <t xml:space="preserve">mecher 2023-דירה 36 טיפוס D1</t>
+          <t xml:space="preserve">mecher 2023-דירות 4-14-24-34-44-54-64 טיפוס B2</t>
         </is>
       </c>
       <c r="F9" s="65">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G9" s="65">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H9" s="65">
-        <v>89</v>
-      </c>
-      <c r="I9" s="65">
-        <v>0</v>
+        <v>53</v>
+      </c>
+      <c t="n" r="I9">
+        <v>6.5</v>
       </c>
       <c t="inlineStr" r="L9">
         <is>
-          <t xml:space="preserve">מזרח </t>
-        </is>
-      </c>
-      <c r="N9" s="65">
-        <v>0</v>
-      </c>
-      <c r="O9" s="65">
-        <v>0</v>
+          <t xml:space="preserve">צפון </t>
+        </is>
+      </c>
+      <c r="N9" s="63">
+        <v>4270000</v>
+      </c>
+      <c r="O9" s="63">
+        <v>4270000</v>
       </c>
       <c t="inlineStr" r="R9">
         <is>
@@ -717,7 +699,7 @@
         <v>15</v>
       </c>
       <c r="C10" s="65">
-        <v>37</v>
+        <v>65</v>
       </c>
       <c t="inlineStr" r="D10">
         <is>
@@ -726,31 +708,31 @@
       </c>
       <c t="inlineStr" r="E10">
         <is>
-          <t xml:space="preserve">mecher 2023-דירות 37-47-57-67 טיפוס E2</t>
+          <t xml:space="preserve">mecher 2023-דירות 5-15-25-35-45-55-65 טיפוס C</t>
         </is>
       </c>
       <c r="F10" s="65">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G10" s="65">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H10" s="65">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c t="n" r="I10">
-        <v>10.1</v>
+        <v>6.9</v>
       </c>
       <c t="inlineStr" r="L10">
         <is>
-          <t xml:space="preserve">דרום מזרח </t>
+          <t xml:space="preserve">מזרח </t>
         </is>
       </c>
       <c r="N10" s="63">
-        <v>5810000</v>
+        <v>7310000</v>
       </c>
       <c r="O10" s="63">
-        <v>5810000</v>
+        <v>7310000</v>
       </c>
       <c t="inlineStr" r="R10">
         <is>
@@ -768,7 +750,7 @@
         <v>15</v>
       </c>
       <c r="C11" s="65">
-        <v>38</v>
+        <v>66</v>
       </c>
       <c t="inlineStr" r="D11">
         <is>
@@ -777,31 +759,31 @@
       </c>
       <c t="inlineStr" r="E11">
         <is>
-          <t xml:space="preserve">mecher 2023-דירות 38-48-58-68 טיפוס F3</t>
+          <t xml:space="preserve">mecher 2023-דירות 46-56-66 טיפוס D2</t>
         </is>
       </c>
       <c r="F11" s="65">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G11" s="65">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H11" s="65">
-        <v>53</v>
+        <v>89</v>
       </c>
       <c t="n" r="I11">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c t="inlineStr" r="L11">
         <is>
-          <t xml:space="preserve">דרום </t>
+          <t xml:space="preserve">מזרח </t>
         </is>
       </c>
       <c r="N11" s="63">
-        <v>4030000</v>
+        <v>7400000</v>
       </c>
       <c r="O11" s="63">
-        <v>4030000</v>
+        <v>7400000</v>
       </c>
       <c t="inlineStr" r="R11">
         <is>
@@ -819,7 +801,7 @@
         <v>15</v>
       </c>
       <c r="C12" s="65">
-        <v>39</v>
+        <v>67</v>
       </c>
       <c t="inlineStr" r="D12">
         <is>
@@ -828,31 +810,31 @@
       </c>
       <c t="inlineStr" r="E12">
         <is>
-          <t xml:space="preserve">mecher 2023-דירות 39-49-59-69 טיפוס G2</t>
+          <t xml:space="preserve">mecher 2023-דירות 37-47-57-67 טיפוס E2</t>
         </is>
       </c>
       <c r="F12" s="65">
+        <v>7</v>
+      </c>
+      <c r="G12" s="65">
         <v>4</v>
       </c>
-      <c r="G12" s="65">
-        <v>2</v>
-      </c>
       <c r="H12" s="65">
-        <v>54</v>
+        <v>89</v>
       </c>
       <c t="n" r="I12">
-        <v>4.2</v>
+        <v>10.1</v>
       </c>
       <c t="inlineStr" r="L12">
         <is>
-          <t xml:space="preserve">דרום </t>
-        </is>
-      </c>
-      <c r="N12" s="65">
-        <v>0</v>
-      </c>
-      <c r="O12" s="65">
-        <v>0</v>
+          <t xml:space="preserve">דרום מזרח </t>
+        </is>
+      </c>
+      <c r="N12" s="63">
+        <v>7600000</v>
+      </c>
+      <c r="O12" s="63">
+        <v>7600000</v>
       </c>
       <c t="inlineStr" r="R12">
         <is>
@@ -870,7 +852,7 @@
         <v>15</v>
       </c>
       <c r="C13" s="65">
-        <v>40</v>
+        <v>68</v>
       </c>
       <c t="inlineStr" r="D13">
         <is>
@@ -879,31 +861,31 @@
       </c>
       <c t="inlineStr" r="E13">
         <is>
-          <t xml:space="preserve">mecher 2023-דירות 40,50,60,70 טיפוס H2</t>
+          <t xml:space="preserve">mecher 2023-דירות 38-48-58-68 טיפוס F3</t>
         </is>
       </c>
       <c r="F13" s="65">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G13" s="65">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H13" s="65">
-        <v>93</v>
+        <v>53</v>
       </c>
       <c t="n" r="I13">
-        <v>8.1</v>
+        <v>5.9</v>
       </c>
       <c t="inlineStr" r="L13">
         <is>
-          <t xml:space="preserve">דרום מערב </t>
+          <t xml:space="preserve">דרום </t>
         </is>
       </c>
       <c r="N13" s="63">
-        <v>5550000</v>
+        <v>4550000</v>
       </c>
       <c r="O13" s="63">
-        <v>5550000</v>
+        <v>4550000</v>
       </c>
       <c t="inlineStr" r="R13">
         <is>
@@ -921,7 +903,7 @@
         <v>15</v>
       </c>
       <c r="C14" s="65">
-        <v>41</v>
+        <v>69</v>
       </c>
       <c t="inlineStr" r="D14">
         <is>
@@ -930,31 +912,31 @@
       </c>
       <c t="inlineStr" r="E14">
         <is>
-          <t xml:space="preserve">mecher 2023-דירות 1-11-21-31-41-51-61 טיפוס A</t>
+          <t xml:space="preserve">mecher 2023-דירות 39-49-59-69 טיפוס G2</t>
         </is>
       </c>
       <c r="F14" s="65">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G14" s="65">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H14" s="65">
-        <v>88</v>
+        <v>54</v>
       </c>
       <c t="n" r="I14">
-        <v>6.4</v>
+        <v>4.2</v>
       </c>
       <c t="inlineStr" r="L14">
         <is>
-          <t xml:space="preserve">צפון מערב </t>
+          <t xml:space="preserve">דרום </t>
         </is>
       </c>
       <c r="N14" s="63">
-        <v>5360000</v>
+        <v>4540000</v>
       </c>
       <c r="O14" s="63">
-        <v>5360000</v>
+        <v>4540000</v>
       </c>
       <c t="inlineStr" r="R14">
         <is>
@@ -972,7 +954,7 @@
         <v>15</v>
       </c>
       <c r="C15" s="65">
-        <v>42</v>
+        <v>70</v>
       </c>
       <c t="inlineStr" r="D15">
         <is>
@@ -981,31 +963,31 @@
       </c>
       <c t="inlineStr" r="E15">
         <is>
-          <t xml:space="preserve">mecher 2023-דירות 2-12-22-32-42-52-62 טיפוס B</t>
+          <t xml:space="preserve">mecher 2023-דירות 40,50,60,70 טיפוס H2</t>
         </is>
       </c>
       <c r="F15" s="65">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G15" s="65">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H15" s="65">
-        <v>53</v>
+        <v>93</v>
       </c>
       <c t="n" r="I15">
-        <v>6.5</v>
+        <v>8.1</v>
       </c>
       <c t="inlineStr" r="L15">
         <is>
-          <t xml:space="preserve">צפון </t>
+          <t xml:space="preserve">דרום מערב </t>
         </is>
       </c>
       <c r="N15" s="63">
-        <v>3940000</v>
+        <v>7890000</v>
       </c>
       <c r="O15" s="63">
-        <v>3940000</v>
+        <v>7890000</v>
       </c>
       <c t="inlineStr" r="R15">
         <is>
@@ -1023,40 +1005,35 @@
         <v>15</v>
       </c>
       <c r="C16" s="65">
-        <v>43</v>
+        <v>71</v>
       </c>
       <c t="inlineStr" r="D16">
         <is>
           <t xml:space="preserve">דירה</t>
         </is>
       </c>
-      <c t="inlineStr" r="E16">
-        <is>
-          <t xml:space="preserve">mecher 2023-דירות 3-13-23-33-43-53-63 טיפוס B1</t>
-        </is>
-      </c>
       <c r="F16" s="65">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G16" s="65">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H16" s="65">
-        <v>53</v>
-      </c>
-      <c t="n" r="I16">
-        <v>6.5</v>
+        <v>166</v>
+      </c>
+      <c r="I16" s="65">
+        <v>14</v>
       </c>
       <c t="inlineStr" r="L16">
         <is>
-          <t xml:space="preserve">צפון </t>
+          <t xml:space="preserve">צפון דרום מערב </t>
         </is>
       </c>
       <c r="N16" s="63">
-        <v>3940000</v>
+        <v>15750000</v>
       </c>
       <c r="O16" s="63">
-        <v>3940000</v>
+        <v>15750000</v>
       </c>
       <c t="inlineStr" r="R16">
         <is>
@@ -1074,29 +1051,24 @@
         <v>15</v>
       </c>
       <c r="C17" s="65">
-        <v>44</v>
+        <v>72</v>
       </c>
       <c t="inlineStr" r="D17">
         <is>
           <t xml:space="preserve">דירה</t>
         </is>
       </c>
-      <c t="inlineStr" r="E17">
-        <is>
-          <t xml:space="preserve">mecher 2023-דירות 4-14-24-34-44-54-64 טיפוס B2</t>
-        </is>
-      </c>
       <c r="F17" s="65">
+        <v>8</v>
+      </c>
+      <c r="G17" s="65">
         <v>5</v>
       </c>
-      <c r="G17" s="65">
-        <v>2</v>
-      </c>
       <c r="H17" s="65">
-        <v>53</v>
-      </c>
-      <c t="n" r="I17">
-        <v>6.5</v>
+        <v>150</v>
+      </c>
+      <c r="I17" s="65">
+        <v>14</v>
       </c>
       <c t="inlineStr" r="L17">
         <is>
@@ -1104,10 +1076,10 @@
         </is>
       </c>
       <c r="N17" s="63">
-        <v>3940000</v>
+        <v>14320000</v>
       </c>
       <c r="O17" s="63">
-        <v>3940000</v>
+        <v>14320000</v>
       </c>
       <c t="inlineStr" r="R17">
         <is>
@@ -1125,40 +1097,35 @@
         <v>15</v>
       </c>
       <c r="C18" s="65">
-        <v>45</v>
+        <v>73</v>
       </c>
       <c t="inlineStr" r="D18">
         <is>
           <t xml:space="preserve">דירה</t>
         </is>
       </c>
-      <c t="inlineStr" r="E18">
-        <is>
-          <t xml:space="preserve">mecher 2023-דירות 5-15-25-35-45-55-65 טיפוס C</t>
-        </is>
-      </c>
       <c r="F18" s="65">
+        <v>8</v>
+      </c>
+      <c r="G18" s="65">
         <v>5</v>
       </c>
-      <c r="G18" s="65">
-        <v>3</v>
-      </c>
       <c r="H18" s="65">
-        <v>87</v>
-      </c>
-      <c t="n" r="I18">
-        <v>6.9</v>
+        <v>150</v>
+      </c>
+      <c r="I18" s="65">
+        <v>28</v>
       </c>
       <c t="inlineStr" r="L18">
         <is>
-          <t xml:space="preserve">מזרח </t>
+          <t xml:space="preserve">צפון </t>
         </is>
       </c>
       <c r="N18" s="63">
-        <v>5800000</v>
+        <v>14900000</v>
       </c>
       <c r="O18" s="63">
-        <v>5800000</v>
+        <v>14900000</v>
       </c>
       <c t="inlineStr" r="R18">
         <is>
@@ -1176,40 +1143,35 @@
         <v>15</v>
       </c>
       <c r="C19" s="65">
-        <v>46</v>
+        <v>74</v>
       </c>
       <c t="inlineStr" r="D19">
         <is>
           <t xml:space="preserve">דירה</t>
         </is>
       </c>
-      <c t="inlineStr" r="E19">
-        <is>
-          <t xml:space="preserve">mecher 2023-דירות 46-56-66 טיפוס D2</t>
-        </is>
-      </c>
       <c r="F19" s="65">
+        <v>8</v>
+      </c>
+      <c r="G19" s="65">
         <v>5</v>
       </c>
-      <c r="G19" s="65">
-        <v>3</v>
-      </c>
       <c r="H19" s="65">
-        <v>89</v>
-      </c>
-      <c t="n" r="I19">
-        <v>6.2</v>
+        <v>164</v>
+      </c>
+      <c r="I19" s="65">
+        <v>86</v>
       </c>
       <c t="inlineStr" r="L19">
         <is>
-          <t xml:space="preserve">מזרח </t>
+          <t xml:space="preserve">צפון מזרח </t>
         </is>
       </c>
       <c r="N19" s="63">
-        <v>5200000</v>
+        <v>19700000</v>
       </c>
       <c r="O19" s="63">
-        <v>5200000</v>
+        <v>19700000</v>
       </c>
       <c t="inlineStr" r="R19">
         <is>
@@ -1227,40 +1189,35 @@
         <v>15</v>
       </c>
       <c r="C20" s="65">
-        <v>47</v>
+        <v>75</v>
       </c>
       <c t="inlineStr" r="D20">
         <is>
           <t xml:space="preserve">דירה</t>
         </is>
       </c>
-      <c t="inlineStr" r="E20">
-        <is>
-          <t xml:space="preserve">mecher 2023-דירות 37-47-57-67 טיפוס E2</t>
-        </is>
-      </c>
       <c r="F20" s="65">
+        <v>8</v>
+      </c>
+      <c r="G20" s="65">
         <v>5</v>
       </c>
-      <c r="G20" s="65">
-        <v>4</v>
-      </c>
       <c r="H20" s="65">
-        <v>89</v>
-      </c>
-      <c t="n" r="I20">
-        <v>10.1</v>
+        <v>162</v>
+      </c>
+      <c r="I20" s="65">
+        <v>64</v>
       </c>
       <c t="inlineStr" r="L20">
         <is>
-          <t xml:space="preserve">דרום מזרח </t>
+          <t xml:space="preserve">מזרח </t>
         </is>
       </c>
       <c r="N20" s="63">
-        <v>5520000</v>
+        <v>18580000</v>
       </c>
       <c r="O20" s="63">
-        <v>5520000</v>
+        <v>18580000</v>
       </c>
       <c t="inlineStr" r="R20">
         <is>
@@ -1278,40 +1235,35 @@
         <v>15</v>
       </c>
       <c r="C21" s="65">
-        <v>48</v>
+        <v>76</v>
       </c>
       <c t="inlineStr" r="D21">
         <is>
           <t xml:space="preserve">דירה</t>
         </is>
       </c>
-      <c t="inlineStr" r="E21">
-        <is>
-          <t xml:space="preserve">mecher 2023-דירות 38-48-58-68 טיפוס F3</t>
-        </is>
-      </c>
       <c r="F21" s="65">
+        <v>8</v>
+      </c>
+      <c r="G21" s="65">
         <v>5</v>
       </c>
-      <c r="G21" s="65">
-        <v>2</v>
-      </c>
       <c r="H21" s="65">
-        <v>53</v>
-      </c>
-      <c t="n" r="I21">
-        <v>5.9</v>
+        <v>166</v>
+      </c>
+      <c r="I21" s="65">
+        <v>86</v>
       </c>
       <c t="inlineStr" r="L21">
         <is>
-          <t xml:space="preserve">דרום </t>
+          <t xml:space="preserve">דרום מזרח </t>
         </is>
       </c>
       <c r="N21" s="63">
-        <v>3900000</v>
+        <v>19950000</v>
       </c>
       <c r="O21" s="63">
-        <v>3900000</v>
+        <v>19950000</v>
       </c>
       <c t="inlineStr" r="R21">
         <is>
@@ -1329,29 +1281,24 @@
         <v>15</v>
       </c>
       <c r="C22" s="65">
-        <v>49</v>
+        <v>77</v>
       </c>
       <c t="inlineStr" r="D22">
         <is>
           <t xml:space="preserve">דירה</t>
         </is>
       </c>
-      <c t="inlineStr" r="E22">
-        <is>
-          <t xml:space="preserve">mecher 2023-דירות 39-49-59-69 טיפוס G2</t>
-        </is>
-      </c>
       <c r="F22" s="65">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G22" s="65">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H22" s="65">
-        <v>54</v>
-      </c>
-      <c t="n" r="I22">
-        <v>4.2</v>
+        <v>200</v>
+      </c>
+      <c r="I22" s="65">
+        <v>62</v>
       </c>
       <c t="inlineStr" r="L22">
         <is>
@@ -1359,10 +1306,10 @@
         </is>
       </c>
       <c r="N22" s="63">
-        <v>4210000</v>
+        <v>21920000</v>
       </c>
       <c r="O22" s="63">
-        <v>4210000</v>
+        <v>21920000</v>
       </c>
       <c t="inlineStr" r="R22">
         <is>
@@ -1380,29 +1327,24 @@
         <v>15</v>
       </c>
       <c r="C23" s="65">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c t="inlineStr" r="D23">
         <is>
           <t xml:space="preserve">דירה</t>
         </is>
       </c>
-      <c t="inlineStr" r="E23">
-        <is>
-          <t xml:space="preserve">mecher 2023-דירות 40,50,60,70 טיפוס H2</t>
-        </is>
-      </c>
       <c r="F23" s="65">
+        <v>8</v>
+      </c>
+      <c r="G23" s="65">
         <v>5</v>
       </c>
-      <c r="G23" s="65">
-        <v>4</v>
-      </c>
       <c r="H23" s="65">
-        <v>93</v>
-      </c>
-      <c t="n" r="I23">
-        <v>8.1</v>
+        <v>168</v>
+      </c>
+      <c r="I23" s="65">
+        <v>18</v>
       </c>
       <c t="inlineStr" r="L23">
         <is>
@@ -1410,79 +1352,58 @@
         </is>
       </c>
       <c r="N23" s="63">
-        <v>5700000</v>
+        <v>16690000</v>
       </c>
       <c r="O23" s="63">
-        <v>5700000</v>
-      </c>
-      <c r="P23" s="63">
-        <v>6990000</v>
-      </c>
-      <c t="inlineStr" r="Q23">
-        <is>
-          <t xml:space="preserve">הרשמה: משה</t>
-        </is>
+        <v>16690000</v>
       </c>
       <c t="inlineStr" r="R23">
         <is>
-          <t xml:space="preserve">הרשמה</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="S23">
-        <is>
-          <t xml:space="preserve">אהרון אברהם</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="T23">
-        <is>
-          <t xml:space="preserve">24/05/2026</t>
+          <t xml:space="preserve">פעיל</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c t="inlineStr" r="A24">
         <is>
-          <t xml:space="preserve">עדן</t>
-        </is>
-      </c>
-      <c r="B24" s="65">
-        <v>15</v>
+          <t xml:space="preserve">שמואל הנגיד-רזדנס</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="B24">
+        <is>
+          <t xml:space="preserve">27-1</t>
+        </is>
       </c>
       <c r="C24" s="65">
-        <v>51</v>
+        <v>1</v>
       </c>
       <c t="inlineStr" r="D24">
         <is>
-          <t xml:space="preserve">דירה</t>
+          <t xml:space="preserve">דירת גן</t>
         </is>
       </c>
       <c t="inlineStr" r="E24">
         <is>
-          <t xml:space="preserve">mecher 2023-דירות 1-11-21-31-41-51-61 טיפוס A</t>
+          <t xml:space="preserve">b1 apt 1</t>
         </is>
       </c>
       <c r="F24" s="65">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G24" s="65">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H24" s="65">
-        <v>88</v>
-      </c>
-      <c t="n" r="I24">
-        <v>6.4</v>
-      </c>
-      <c t="inlineStr" r="L24">
-        <is>
-          <t xml:space="preserve">צפון מערב </t>
-        </is>
+        <v>69</v>
+      </c>
+      <c r="I24" s="65">
+        <v>35</v>
       </c>
       <c r="N24" s="63">
-        <v>5510000</v>
+        <v>4530240</v>
       </c>
       <c r="O24" s="63">
-        <v>5510000</v>
+        <v>4530240</v>
       </c>
       <c t="inlineStr" r="R24">
         <is>
@@ -1493,14 +1414,16 @@
     <row r="25">
       <c t="inlineStr" r="A25">
         <is>
-          <t xml:space="preserve">עדן</t>
-        </is>
-      </c>
-      <c r="B25" s="65">
-        <v>15</v>
+          <t xml:space="preserve">שמואל הנגיד-רזדנס</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="B25">
+        <is>
+          <t xml:space="preserve">27-1</t>
+        </is>
       </c>
       <c r="C25" s="65">
-        <v>52</v>
+        <v>2</v>
       </c>
       <c t="inlineStr" r="D25">
         <is>
@@ -1509,49 +1432,46 @@
       </c>
       <c t="inlineStr" r="E25">
         <is>
-          <t xml:space="preserve">mecher 2023-דירות 2-12-22-32-42-52-62 טיפוס B</t>
+          <t xml:space="preserve">b1 apt 2</t>
         </is>
       </c>
       <c r="F25" s="65">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G25" s="65">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H25" s="65">
-        <v>53</v>
-      </c>
-      <c t="n" r="I25">
-        <v>6.5</v>
-      </c>
-      <c t="inlineStr" r="L25">
-        <is>
-          <t xml:space="preserve">צפון </t>
-        </is>
+        <v>76</v>
+      </c>
+      <c r="I25" s="65">
+        <v>7</v>
       </c>
       <c r="N25" s="63">
-        <v>4100000</v>
+        <v>4293000</v>
       </c>
       <c r="O25" s="63">
-        <v>4100000</v>
+        <v>4293000</v>
       </c>
       <c t="inlineStr" r="R25">
         <is>
-          <t xml:space="preserve">פעיל</t>
+          <t xml:space="preserve">מו״מ</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c t="inlineStr" r="A26">
         <is>
-          <t xml:space="preserve">עדן</t>
-        </is>
-      </c>
-      <c r="B26" s="65">
-        <v>15</v>
+          <t xml:space="preserve">שמואל הנגיד-רזדנס</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="B26">
+        <is>
+          <t xml:space="preserve">27-1</t>
+        </is>
       </c>
       <c r="C26" s="65">
-        <v>53</v>
+        <v>3</v>
       </c>
       <c t="inlineStr" r="D26">
         <is>
@@ -1560,31 +1480,26 @@
       </c>
       <c t="inlineStr" r="E26">
         <is>
-          <t xml:space="preserve">mecher 2023-דירות 3-13-23-33-43-53-63 טיפוס B1</t>
+          <t xml:space="preserve">b1 apt 3</t>
         </is>
       </c>
       <c r="F26" s="65">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G26" s="65">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H26" s="65">
-        <v>53</v>
-      </c>
-      <c t="n" r="I26">
-        <v>6.5</v>
-      </c>
-      <c t="inlineStr" r="L26">
-        <is>
-          <t xml:space="preserve">צפון </t>
-        </is>
+        <v>75</v>
+      </c>
+      <c r="I26" s="65">
+        <v>10</v>
       </c>
       <c r="N26" s="63">
-        <v>4110000</v>
+        <v>4320000</v>
       </c>
       <c r="O26" s="63">
-        <v>4110000</v>
+        <v>4320000</v>
       </c>
       <c t="inlineStr" r="R26">
         <is>
@@ -1595,14 +1510,16 @@
     <row r="27">
       <c t="inlineStr" r="A27">
         <is>
-          <t xml:space="preserve">עדן</t>
-        </is>
-      </c>
-      <c r="B27" s="65">
-        <v>15</v>
+          <t xml:space="preserve">שמואל הנגיד-רזדנס</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="B27">
+        <is>
+          <t xml:space="preserve">27-1</t>
+        </is>
       </c>
       <c r="C27" s="65">
-        <v>54</v>
+        <v>4</v>
       </c>
       <c t="inlineStr" r="D27">
         <is>
@@ -1611,31 +1528,26 @@
       </c>
       <c t="inlineStr" r="E27">
         <is>
-          <t xml:space="preserve">mecher 2023-דירות 4-14-24-34-44-54-64 טיפוס B2</t>
+          <t xml:space="preserve">b1 apt 4</t>
         </is>
       </c>
       <c r="F27" s="65">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G27" s="65">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H27" s="65">
-        <v>53</v>
-      </c>
-      <c t="n" r="I27">
-        <v>6.5</v>
-      </c>
-      <c t="inlineStr" r="L27">
-        <is>
-          <t xml:space="preserve">צפון </t>
-        </is>
+        <v>76</v>
+      </c>
+      <c r="I27" s="65">
+        <v>7</v>
       </c>
       <c r="N27" s="63">
-        <v>4100000</v>
+        <v>4378860</v>
       </c>
       <c r="O27" s="63">
-        <v>4100000</v>
+        <v>4378860</v>
       </c>
       <c t="inlineStr" r="R27">
         <is>
